--- a/data-manipulation-scripts/sheets-cleanup/sheets/KIT-A.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/KIT-A.xlsx
@@ -28,19 +28,19 @@
     <t>7899641838966</t>
   </si>
   <si>
-    <t>KIT-A VEDAMOTOS TWISTER CBX250/ TORNADO XR250</t>
+    <t>KIT-A CABEÇOTE  VEDAMOTOS TWISTER CBX250/ TORNADO XR250</t>
   </si>
   <si>
     <t>7899641811785</t>
   </si>
   <si>
-    <t>KIT-A VEDAMOTOS FAN TITAN CG125 2009/ CBF125</t>
+    <t>KIT-A CABEÇOTE  VEDAMOTOS FAN TITAN CG125 2009/ CBF125</t>
   </si>
   <si>
     <t>7899641814953</t>
   </si>
   <si>
-    <t>KIT-A VEDAMOTOS TITAN FAN150 2004/ BROS NXR150 2006 FLEX</t>
+    <t>KIT-A CABEÇOTE  VEDAMOTOS TITAN FAN150 2004/ BROS NXR150 2006 FLEX</t>
   </si>
   <si>
     <t>7899641813260</t>
@@ -49,133 +49,133 @@
     <t>7899641801458</t>
   </si>
   <si>
-    <t>KIT-A VEDAMOTOS TITAN CG 2000 KS ES</t>
+    <t>KIT-A CABEÇOTE  VEDAMOTOS TITAN CG 2000 KS ES</t>
   </si>
   <si>
     <t>7908429139963</t>
   </si>
   <si>
-    <t>KIT-A EMBUS POP110I 2016 A 2023/ BIZ110I 2016 A 2023</t>
+    <t>KIT-A CABEÇOTE  EMBUS POP110I 2016 A 2023/ BIZ110I 2016 A 2023</t>
   </si>
   <si>
     <t>7908429112164</t>
   </si>
   <si>
-    <t>KIT-A EMBUS FACTOR FAZER XTZ150 2014 A 2020</t>
+    <t>KIT-A CABEÇOTE  EMBUS FACTOR FAZER XTZ150 2014 A 2020</t>
   </si>
   <si>
     <t>7899641815578</t>
   </si>
   <si>
-    <t>KIT-A VEDAMOTOS FAZER YS250</t>
+    <t>KIT-A CABEÇOTE  VEDAMOTOS FAZER YS250</t>
   </si>
   <si>
     <t>7899641859657</t>
   </si>
   <si>
-    <t>KIT-A VEDAMOTOS CB250F TWISTER 2016</t>
+    <t>KIT-A CABEÇOTE  VEDAMOTOS CB250F TWISTER 2016</t>
   </si>
   <si>
     <t>6942234802163</t>
   </si>
   <si>
-    <t>KIT-A BRAVIC TITAN FAN160 2016 A 2021 BMA48112</t>
+    <t>KIT-A CABEÇOTE  BRAVIC TITAN FAN160 2016 A 2021 BMA48112</t>
   </si>
   <si>
     <t>7895443560203</t>
   </si>
   <si>
-    <t>KIT-A VALFLEX CB300 2009 A 2015</t>
+    <t>KIT-A CABEÇOTE  VALFLEX CB300 2009 A 2015</t>
   </si>
   <si>
     <t>7895443563815</t>
   </si>
   <si>
-    <t>KIT-A VALFLEX TITAN 2000 KS ES</t>
+    <t>KIT-A CABEÇOTE  VALFLEX TITAN 2000 KS ES</t>
   </si>
   <si>
     <t>0751320978639</t>
   </si>
   <si>
-    <t>KIT-A IRON SUSUKI YES125 176266</t>
+    <t>KIT-A CABEÇOTE  IRON SUSUKI YES125 176266</t>
   </si>
   <si>
     <t>7899641837235</t>
   </si>
   <si>
-    <t>KIT-A VEDAMOTOS YS FAZER XTZ CROSSER 150 2016</t>
+    <t>KIT-A CABEÇOTE  VEDAMOTOS YS FAZER XTZ CROSSER 150 2016</t>
   </si>
   <si>
     <t>7899641851231</t>
   </si>
   <si>
-    <t xml:space="preserve">KIT-A VEDAMOTOS BROS NXR CG TITAN FAN160 </t>
+    <t xml:space="preserve">KIT-A CABEÇOTE  VEDAMOTOS BROS NXR CG TITAN FAN160 </t>
   </si>
   <si>
     <t>7908429112195</t>
   </si>
   <si>
-    <t xml:space="preserve">KIT-A EMBUS POP110I/ BIZ110I </t>
+    <t xml:space="preserve">KIT-A CABEÇOTE  EMBUS POP110I/ BIZ110I </t>
   </si>
   <si>
     <t>7899248134676</t>
   </si>
   <si>
-    <t>KIT-A JAPAN CB300/ XRE300</t>
+    <t>KIT-A CABEÇOTE  WW3 CB300/ XRE300</t>
   </si>
   <si>
     <t>7899248134683</t>
   </si>
   <si>
-    <t>KIT-A JAPAN TWISTER CBX250/ XR 250 TORNADO</t>
+    <t>KIT-A CABEÇOTE  JAPAN TWISTER CBX250/ XR 250 TORNADO</t>
   </si>
   <si>
     <t>7899248134720</t>
   </si>
   <si>
-    <t>KIT-A JAPAN TITAN FAN CG150 1104015</t>
+    <t>KIT-A CABEÇOTE  JAPAN TITAN FAN CG150 1104015</t>
   </si>
   <si>
     <t>7899248163317</t>
   </si>
   <si>
-    <t>KIT-A JAPAN CG125 1992 A 1998/ TITAN 2000 KS 1104225</t>
+    <t>KIT-A CABEÇOTE  JAPAN CG125 1992 A 1998/ TITAN 2000 KS 1104225</t>
   </si>
   <si>
     <t>7899248134713</t>
   </si>
   <si>
-    <t>KIT-A JAPAN FAN CG125 2000 A 2006 1104015</t>
+    <t>KIT-A CABEÇOTE  JAPAN FAN CG125 2000 A 2006 1104015</t>
   </si>
   <si>
     <t>7899248134669</t>
   </si>
   <si>
-    <t>KIT-A JAPAN BIZ125 1104010</t>
+    <t>KIT-A CABEÇOTE  JAPAN BIZ125 1104010</t>
   </si>
   <si>
     <t>7899248174658</t>
   </si>
   <si>
-    <t>KIT-A JAPAN SUSUKI YES125 1250308</t>
+    <t>KIT-A CABEÇOTE  JAPAN SUSUKI YES125 1250308</t>
   </si>
   <si>
     <t>7899248167146</t>
   </si>
   <si>
-    <t>KIT-A JAPAN FAZER150 1211850</t>
+    <t>KIT-A CABEÇOTE  JAPAN FAZER150 1211850</t>
   </si>
   <si>
     <t>7909201039570</t>
   </si>
   <si>
-    <t>KIT-A JAPAN BIZ110 2015 1105248</t>
+    <t>KIT-A CABEÇOTE  JAPAN BIZ110 2015 1105248</t>
   </si>
   <si>
     <t>7893986251862</t>
   </si>
   <si>
-    <t>KIT-A PEÇA+ CG 1992/ TITAN 2000 KS/ BROX NXR125</t>
+    <t>KIT-A CABEÇOTE  PEÇA+ CG 1992/ TITAN 2000 KS/ BROX NXR125</t>
   </si>
 </sst>
 </file>
@@ -227,10 +227,10 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -497,10 +497,12 @@
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>5.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4">
+        <v>50.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -531,10 +533,12 @@
       <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>9.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -565,10 +569,12 @@
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>5.0</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -596,13 +602,15 @@
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="7">
         <v>5.0</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -630,13 +638,15 @@
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="7">
         <v>4.0</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -664,13 +674,15 @@
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="7">
         <v>3.0</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -698,7 +710,7 @@
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="7">
@@ -734,13 +746,15 @@
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="7">
         <v>1.0</v>
       </c>
-      <c r="D9" s="6"/>
+      <c r="D9" s="4">
+        <v>50.0</v>
+      </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -768,7 +782,7 @@
       <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="7">
@@ -804,7 +818,7 @@
       <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="7">
@@ -840,13 +854,15 @@
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="7">
         <v>3.0</v>
       </c>
-      <c r="D12" s="6"/>
+      <c r="D12" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
@@ -874,13 +890,15 @@
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="7">
         <v>6.0</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
@@ -908,7 +926,7 @@
       <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="7">
@@ -944,13 +962,15 @@
       <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="7">
         <v>5.0</v>
       </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="4">
+        <v>50.0</v>
+      </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
@@ -978,13 +998,15 @@
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="7">
         <v>2.0</v>
       </c>
-      <c r="D16" s="6"/>
+      <c r="D16" s="4">
+        <v>50.0</v>
+      </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
@@ -1012,13 +1034,15 @@
       <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C17" s="7">
         <v>1.0</v>
       </c>
-      <c r="D17" s="6"/>
+      <c r="D17" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
@@ -1046,13 +1070,15 @@
       <c r="A18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C18" s="7">
         <v>5.0</v>
       </c>
-      <c r="D18" s="6"/>
+      <c r="D18" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
@@ -1080,13 +1106,15 @@
       <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C19" s="7">
         <v>4.0</v>
       </c>
-      <c r="D19" s="6"/>
+      <c r="D19" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
@@ -1114,13 +1142,15 @@
       <c r="A20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C20" s="7">
         <v>7.0</v>
       </c>
-      <c r="D20" s="6"/>
+      <c r="D20" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
@@ -1148,13 +1178,15 @@
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C21" s="7">
         <v>5.0</v>
       </c>
-      <c r="D21" s="6"/>
+      <c r="D21" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
@@ -1182,13 +1214,15 @@
       <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C22" s="7">
         <v>1.0</v>
       </c>
-      <c r="D22" s="6"/>
+      <c r="D22" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -1216,13 +1250,15 @@
       <c r="A23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C23" s="7">
         <v>1.0</v>
       </c>
-      <c r="D23" s="6"/>
+      <c r="D23" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -1250,13 +1286,15 @@
       <c r="A24" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C24" s="7">
         <v>1.0</v>
       </c>
-      <c r="D24" s="6"/>
+      <c r="D24" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -1284,13 +1322,15 @@
       <c r="A25" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C25" s="7">
         <v>1.0</v>
       </c>
-      <c r="D25" s="6"/>
+      <c r="D25" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
@@ -1318,13 +1358,15 @@
       <c r="A26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C26" s="7">
         <v>1.0</v>
       </c>
-      <c r="D26" s="6"/>
+      <c r="D26" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
@@ -1352,13 +1394,15 @@
       <c r="A27" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C27" s="7">
         <v>1.0</v>
       </c>
-      <c r="D27" s="6"/>
+      <c r="D27" s="4">
+        <v>30.0</v>
+      </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
